--- a/Masy.xlsx
+++ b/Masy.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tech\robotyka\robots\evangelion-turbo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{419D18CF-9844-4B33-A3DB-B2D0BB99D03A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65C5DD78-DB65-4D1C-A2A6-5F5AA1D8AE0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="480" windowWidth="38640" windowHeight="21240" xr2:uid="{1B89EA85-0D7B-4BD5-90E2-014B62B41C6E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>Nazwa</t>
   </si>
@@ -47,12 +47,6 @@
     <t>Masa [g]</t>
   </si>
   <si>
-    <t>Koło różowe z felgą</t>
-  </si>
-  <si>
-    <t>Masa łączna [g]:</t>
-  </si>
-  <si>
     <t>Felga SLS biała</t>
   </si>
   <si>
@@ -122,15 +116,9 @@
     <t>Left gearbox cover, stal</t>
   </si>
   <si>
-    <t>Controller PCB</t>
-  </si>
-  <si>
     <t>Lipo 3s 450mAh</t>
   </si>
   <si>
-    <t>Motor driver PCB</t>
-  </si>
-  <si>
     <t>Line sensor</t>
   </si>
   <si>
@@ -149,7 +137,22 @@
     <t>Ośka do łożyska pośredniego 2mm</t>
   </si>
   <si>
-    <t>Śruby, kabelki, etc</t>
+    <t>Płóg stal S7</t>
+  </si>
+  <si>
+    <t>Lipo 3S 300mAh</t>
+  </si>
+  <si>
+    <t>Śruby, kabelki, elektronika</t>
+  </si>
+  <si>
+    <t>RAZEM:</t>
+  </si>
+  <si>
+    <t>Ilość 2</t>
+  </si>
+  <si>
+    <t>Koło</t>
   </si>
 </sst>
 </file>
@@ -242,10 +245,10 @@
   </cellStyles>
   <dxfs count="2">
     <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
+      <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -261,12 +264,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EF7A5B60-EA04-4142-B839-02EF6ED8F311}" name="Table1" displayName="Table1" ref="A1:C1048576" totalsRowShown="0">
-  <autoFilter ref="A1:C1048576" xr:uid="{EF7A5B60-EA04-4142-B839-02EF6ED8F311}"/>
-  <tableColumns count="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EF7A5B60-EA04-4142-B839-02EF6ED8F311}" name="Table1" displayName="Table1" ref="A1:D1048576" totalsRowShown="0">
+  <autoFilter ref="A1:D1048576" xr:uid="{EF7A5B60-EA04-4142-B839-02EF6ED8F311}"/>
+  <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{0124A995-F30B-461A-9456-EBD9F58DD7A2}" name="Nazwa"/>
-    <tableColumn id="2" xr3:uid="{3EF73F92-A642-431A-AB3F-F7D05E855204}" name="Masa [g]" dataDxfId="0"/>
-    <tableColumn id="3" xr3:uid="{E01C02C9-E6D1-454E-A3FA-A40F06E416F9}" name="Ilosc" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{3EF73F92-A642-431A-AB3F-F7D05E855204}" name="Masa [g]" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{E01C02C9-E6D1-454E-A3FA-A40F06E416F9}" name="Ilosc" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{918F5BA3-B011-41A7-BEC6-AC260D50B21B}" name="Ilość 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -589,12 +593,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10803BC4-6355-4647-A605-F1E7D1B0F2BA}">
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
     <col min="2" max="2" width="18.28515625" style="3" customWidth="1"/>
     <col min="3" max="3" width="16.140625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" customWidth="1"/>
     <col min="5" max="5" width="17.5703125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -608,40 +613,44 @@
       <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
+      <c r="D1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="B2" s="3">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C2" s="4">
         <v>2</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>4</v>
-      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2"/>
     </row>
     <row r="3" spans="1:5" ht="15.75" thickBot="1">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B3" s="3">
         <f>11.6/4</f>
         <v>2.9</v>
       </c>
       <c r="C3" s="4">
-        <v>2</v>
-      </c>
-      <c r="E3" s="5">
-        <f>SUMPRODUCT(Table1[Masa '[g']],Table1[Ilosc])</f>
-        <v>890.62333333333333</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3" s="5"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B4" s="3">
         <f>2.8/4</f>
@@ -650,10 +659,13 @@
       <c r="C4" s="4">
         <v>2</v>
       </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B5" s="3">
         <f>11.4/5</f>
@@ -662,10 +674,13 @@
       <c r="C5" s="4">
         <v>4</v>
       </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B6" s="3">
         <f>11.6/8</f>
@@ -674,10 +689,13 @@
       <c r="C6" s="4">
         <v>2</v>
       </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B7" s="3">
         <v>86</v>
@@ -685,11 +703,14 @@
       <c r="C7" s="4">
         <v>2</v>
       </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
       <c r="E7" s="1"/>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B8" s="3">
         <v>1.5</v>
@@ -697,10 +718,13 @@
       <c r="C8" s="4">
         <v>4</v>
       </c>
+      <c r="D8">
+        <v>4</v>
+      </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B9" s="3">
         <v>74</v>
@@ -708,10 +732,13 @@
       <c r="C9" s="4">
         <v>1</v>
       </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B10" s="3">
         <f>25.6/4</f>
@@ -720,10 +747,13 @@
       <c r="C10" s="4">
         <v>0</v>
       </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B11" s="3">
         <f>52/3</f>
@@ -732,10 +762,13 @@
       <c r="C11" s="4">
         <v>1</v>
       </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B12" s="3">
         <f>38.6/5</f>
@@ -744,265 +777,350 @@
       <c r="C12" s="4">
         <v>1</v>
       </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B13" s="3">
         <v>30</v>
       </c>
       <c r="C13" s="4">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="B14" s="3">
+        <v>26</v>
+      </c>
+      <c r="C14" s="4">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="3">
         <f>56/4</f>
         <v>14</v>
       </c>
-      <c r="C14" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="3">
+      <c r="C15" s="4">
+        <v>2</v>
+      </c>
+      <c r="D15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3">
         <f>4.5/2</f>
         <v>2.25</v>
       </c>
-      <c r="C15" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" t="s">
+      <c r="C16" s="4">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3">
+        <v>15.8</v>
+      </c>
+      <c r="C17" s="4">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3">
+        <v>136</v>
+      </c>
+      <c r="C18" s="4">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="3">
-        <v>15.8</v>
-      </c>
-      <c r="C16" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
+      <c r="B19" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C19" s="4">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="3">
+        <v>39</v>
+      </c>
+      <c r="C20" s="4">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="3">
-        <v>136</v>
-      </c>
-      <c r="C17" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="3">
+      <c r="B21" s="3">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C18" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" s="3">
+      <c r="C21" s="4">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="3">
         <v>39</v>
       </c>
-      <c r="C19" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
+      <c r="C22" s="4">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="3">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C20" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" s="3">
-        <v>39</v>
-      </c>
-      <c r="C21" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" s="3">
+      <c r="B23" s="3">
         <v>8.1</v>
       </c>
-      <c r="C22" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" s="3">
-        <v>70.5</v>
-      </c>
       <c r="C23" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
       <c r="A24" t="s">
         <v>22</v>
       </c>
       <c r="B24" s="3">
+        <v>70.5</v>
+      </c>
+      <c r="C24" s="4">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" t="s">
+        <v>20</v>
+      </c>
+      <c r="B25" s="3">
         <v>8.1</v>
       </c>
-      <c r="C24" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="3">
+      <c r="C25" s="4">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" s="3">
         <v>70.5</v>
       </c>
-      <c r="C25" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" t="s">
+      <c r="C26" s="4">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="3">
+        <v>1</v>
+      </c>
+      <c r="C27" s="4">
+        <v>4</v>
+      </c>
+      <c r="D27">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" t="s">
         <v>28</v>
       </c>
-      <c r="B26" s="3">
-        <v>10</v>
-      </c>
-      <c r="C26" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" t="s">
-        <v>30</v>
-      </c>
-      <c r="B27" s="3">
-        <v>10</v>
-      </c>
-      <c r="C27" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" t="s">
-        <v>29</v>
-      </c>
       <c r="B28" s="3">
-        <v>39</v>
-      </c>
-      <c r="C28" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" t="s">
-        <v>31</v>
-      </c>
-      <c r="B29" s="3">
-        <v>1</v>
-      </c>
-      <c r="C29" s="4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B30" s="3">
         <f>3.3/2</f>
         <v>1.65</v>
       </c>
-      <c r="C30" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" t="s">
-        <v>33</v>
-      </c>
-      <c r="B31" s="3">
+      <c r="C28" s="4">
+        <v>2</v>
+      </c>
+      <c r="D28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" s="3">
         <f>21.6/2</f>
         <v>10.8</v>
       </c>
-      <c r="C31" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" t="s">
-        <v>34</v>
-      </c>
-      <c r="B32" s="3">
+      <c r="C29" s="4">
+        <v>2</v>
+      </c>
+      <c r="D29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30" s="3">
         <f>6.6/2</f>
         <v>3.3</v>
       </c>
-      <c r="C32" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" t="s">
-        <v>35</v>
-      </c>
-      <c r="B33" s="3">
+      <c r="C30" s="4">
+        <v>2</v>
+      </c>
+      <c r="D30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31" s="3">
         <f>1.6/2</f>
         <v>0.8</v>
       </c>
-      <c r="C33" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" t="s">
-        <v>36</v>
-      </c>
-      <c r="B34" s="3">
+      <c r="C31" s="4">
+        <v>2</v>
+      </c>
+      <c r="D31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32" s="3">
         <f>1/2</f>
         <v>0.5</v>
       </c>
+      <c r="C32" s="4">
+        <v>2</v>
+      </c>
+      <c r="D32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" t="s">
+        <v>26</v>
+      </c>
+      <c r="B33" s="3">
+        <v>39</v>
+      </c>
+      <c r="C33" s="4">
+        <v>0</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34" s="3">
+        <v>22.5</v>
+      </c>
       <c r="C34" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" t="s">
-        <v>37</v>
-      </c>
-      <c r="B38" s="3">
-        <v>50</v>
-      </c>
-      <c r="C38" s="4">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35" s="3">
+        <v>53</v>
+      </c>
+      <c r="C35" s="4">
+        <v>1</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>36</v>
+      </c>
+      <c r="C39" s="3">
+        <f>SUMPRODUCT(B2:B38,C2:C38)</f>
+        <v>845.32333333333338</v>
+      </c>
+      <c r="D39" s="3">
+        <f>SUMPRODUCT(B2:B38,D2:D38)</f>
+        <v>445.59000000000015</v>
       </c>
     </row>
   </sheetData>

--- a/Masy.xlsx
+++ b/Masy.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tech\robotyka\robots\evangelion-turbo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65C5DD78-DB65-4D1C-A2A6-5F5AA1D8AE0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28B8DE79-2804-4C5C-99EA-3809BE1C5062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="480" windowWidth="38640" windowHeight="21240" xr2:uid="{1B89EA85-0D7B-4BD5-90E2-014B62B41C6E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>Nazwa</t>
   </si>
@@ -153,6 +153,9 @@
   </si>
   <si>
     <t>Koło</t>
+  </si>
+  <si>
+    <t>Front mount, Aluminium (teoria)</t>
   </si>
 </sst>
 </file>
@@ -593,7 +596,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10803BC4-6355-4647-A605-F1E7D1B0F2BA}">
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -733,7 +736,7 @@
         <v>1</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -748,7 +751,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -763,7 +766,7 @@
         <v>1</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -821,7 +824,7 @@
         <v>2</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -855,13 +858,13 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="B18" s="3">
-        <v>136</v>
+        <v>50</v>
       </c>
       <c r="C18" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -869,258 +872,272 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="3">
-        <v>4.0999999999999996</v>
+        <v>136</v>
       </c>
       <c r="C19" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B20" s="3">
-        <v>39</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C20" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>4.0999999999999996</v>
+        <v>39</v>
       </c>
       <c r="C21" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B22" s="3">
-        <v>39</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C22" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B23" s="3">
-        <v>8.1</v>
+        <v>39</v>
       </c>
       <c r="C23" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B24" s="3">
-        <v>70.5</v>
+        <v>8.1</v>
       </c>
       <c r="C24" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B25" s="3">
-        <v>8.1</v>
+        <v>70.5</v>
       </c>
       <c r="C25" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B26" s="3">
-        <v>70.5</v>
+        <v>8.1</v>
       </c>
       <c r="C26" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B27" s="3">
-        <v>1</v>
+        <v>70.5</v>
       </c>
       <c r="C27" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D27">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3">
+        <v>1</v>
+      </c>
+      <c r="C28" s="4">
+        <v>4</v>
+      </c>
+      <c r="D28">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B29" s="3">
         <f>3.3/2</f>
         <v>1.65</v>
       </c>
-      <c r="C28" s="4">
-        <v>2</v>
-      </c>
-      <c r="D28">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" t="s">
+      <c r="C29" s="4">
+        <v>2</v>
+      </c>
+      <c r="D29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B30" s="3">
         <f>21.6/2</f>
         <v>10.8</v>
       </c>
-      <c r="C29" s="4">
-        <v>2</v>
-      </c>
-      <c r="D29">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" t="s">
+      <c r="C30" s="4">
+        <v>2</v>
+      </c>
+      <c r="D30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" t="s">
         <v>30</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B31" s="3">
         <f>6.6/2</f>
         <v>3.3</v>
       </c>
-      <c r="C30" s="4">
-        <v>2</v>
-      </c>
-      <c r="D30">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" t="s">
+      <c r="C31" s="4">
+        <v>2</v>
+      </c>
+      <c r="D31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" t="s">
         <v>31</v>
       </c>
-      <c r="B31" s="3">
+      <c r="B32" s="3">
         <f>1.6/2</f>
         <v>0.8</v>
       </c>
-      <c r="C31" s="4">
-        <v>2</v>
-      </c>
-      <c r="D31">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" t="s">
+      <c r="C32" s="4">
+        <v>2</v>
+      </c>
+      <c r="D32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" t="s">
         <v>32</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B33" s="3">
         <f>1/2</f>
         <v>0.5</v>
       </c>
-      <c r="C32" s="4">
-        <v>2</v>
-      </c>
-      <c r="D32">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" t="s">
-        <v>26</v>
-      </c>
-      <c r="B33" s="3">
-        <v>39</v>
-      </c>
       <c r="C33" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B34" s="3">
-        <v>22.5</v>
+        <v>39</v>
       </c>
       <c r="C34" s="4">
         <v>1</v>
       </c>
       <c r="D34">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3">
+        <v>22.5</v>
+      </c>
+      <c r="C35" s="4">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" t="s">
         <v>35</v>
       </c>
-      <c r="B35" s="3">
+      <c r="B36" s="3">
         <v>53</v>
       </c>
-      <c r="C35" s="4">
-        <v>1</v>
-      </c>
-      <c r="D35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" t="s">
+      <c r="C36" s="4">
+        <v>1</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" t="s">
         <v>36</v>
       </c>
-      <c r="C39" s="3">
-        <f>SUMPRODUCT(B2:B38,C2:C38)</f>
-        <v>845.32333333333338</v>
-      </c>
-      <c r="D39" s="3">
-        <f>SUMPRODUCT(B2:B38,D2:D38)</f>
-        <v>445.59000000000015</v>
+      <c r="C40" s="3">
+        <f>SUMPRODUCT(B2:B39,C2:C39)</f>
+        <v>861.82333333333338</v>
+      </c>
+      <c r="D40" s="3">
+        <f>SUMPRODUCT(B2:B39,D2:D39)</f>
+        <v>502.52333333333348</v>
       </c>
     </row>
   </sheetData>
